--- a/RnD/TestingChecklist.xlsx
+++ b/RnD/TestingChecklist.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
   <si>
     <t xml:space="preserve">Property</t>
   </si>
@@ -125,6 +125,12 @@
   </si>
   <si>
     <t xml:space="preserve">user enter wrong password or re-password one twice or more cause submit form with empty pasword and re-password </t>
+  </si>
+  <si>
+    <t xml:space="preserve">When user enter wrong password format or password/repassword not the same. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The password/repassword field empty to re-enter.</t>
   </si>
 </sst>
 </file>
@@ -203,8 +209,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -400,107 +410,107 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -523,59 +533,59 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="33.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -598,23 +608,23 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
@@ -637,34 +647,34 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -687,18 +697,18 @@
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -722,37 +732,37 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -772,17 +782,30 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="112.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="112.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52.31"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>24</v>
       </c>
     </row>

--- a/RnD/TestingChecklist.xlsx
+++ b/RnD/TestingChecklist.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="37">
   <si>
     <t xml:space="preserve">Property</t>
   </si>
@@ -131,6 +131,12 @@
   </si>
   <si>
     <t xml:space="preserve">The password/repassword field empty to re-enter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When user enter wrong password format or password/repassword not the same. User re-enter “password” field only and submit ( but the re-password still different/wrong format)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The system re-display wrong type or missmatch password field</t>
   </si>
 </sst>
 </file>
@@ -782,30 +788,40 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="112.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="159.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="54.96"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>24</v>
       </c>
     </row>
